--- a/test/fixtures/xlsx/containers-refused/containers-refused.xlsx
+++ b/test/fixtures/xlsx/containers-refused/containers-refused.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="36">
   <si>
     <t xml:space="preserve">:table Shop</t>
   </si>
@@ -59,6 +59,15 @@
     <t xml:space="preserve">Bag.Prices.Value</t>
   </si>
   <si>
+    <t xml:space="preserve">Bag.Drops.Key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bag.Drops.Value.ItemId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bag.Drops.Value.Count</t>
+  </si>
+  <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
@@ -71,6 +80,9 @@
     <t xml:space="preserve">100;120</t>
   </si>
   <si>
+    <t xml:space="preserve">101</t>
+  </si>
+  <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
@@ -84,6 +96,30 @@
   </si>
   <si>
     <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Stall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A map written as pairs, with an entry that is not one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bag.Prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Depot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A map whose value is a struct, written as pairs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crate.Drops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1:101</t>
   </si>
 </sst>
 </file>
@@ -128,7 +164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:F9"/>
+  <dimension ref="B2:I25"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -155,6 +191,15 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
@@ -172,6 +217,15 @@
       <c r="F4" t="s">
         <v>12</v>
       </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
@@ -189,6 +243,15 @@
       <c r="F5" t="s">
         <v>12</v>
       </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
@@ -206,47 +269,263 @@
       <c r="F6" t="s">
         <v>9</v>
       </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="C7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
         <v>21</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" t="s">
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
         <v>20</v>
       </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" t="s">
-        <v>23</v>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/test/fixtures/xlsx/containers-refused/containers-refused.xlsx
+++ b/test/fixtures/xlsx/containers-refused/containers-refused.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="39">
   <si>
     <t xml:space="preserve">:table Shop</t>
   </si>
@@ -96,6 +96,15 @@
   </si>
   <si>
     <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
   </si>
   <si>
     <t xml:space="preserve">:table Stall</t>
@@ -164,7 +173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:I25"/>
+  <dimension ref="B2:I26"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -348,69 +357,69 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="s">
+    <row r="10">
+      <c r="C10" t="s">
         <v>28</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
         <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -427,105 +436,128 @@
     </row>
     <row r="16">
       <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="s">
         <v>5</v>
       </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17">
       <c r="C17" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" t="s">
         <v>24</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>20</v>
       </c>
-      <c r="F17" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
         <v>22</v>
       </c>
-      <c r="H17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
+      <c r="H18" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="s">
         <v>5</v>
       </c>
-      <c r="C24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25">
       <c r="C25" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
